--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5bbeae322b864c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7aa66604ff1f41db"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7aa66604ff1f41db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re4eabcd2bd7549c1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re4eabcd2bd7549c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcf59df55c9534c83"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcf59df55c9534c83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcc45f076d4564cef"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcc45f076d4564cef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1fdc975c73b0462b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1fdc975c73b0462b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fd60f78728d4fc1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fd60f78728d4fc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Recd54a6e25be4527"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Recd54a6e25be4527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7df6d3455dba4b9b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7df6d3455dba4b9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85bc826ee22b4352"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85bc826ee22b4352"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f28974effa84b74"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f28974effa84b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ab949c59e8e495a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ab949c59e8e495a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21874e9757e043f4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21874e9757e043f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7db89775b38046e8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7db89775b38046e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53def27d71b5403e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53def27d71b5403e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc690cd67aa99465a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc690cd67aa99465a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5a1e1bb7082e4705"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_FormulaRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5a1e1bb7082e4705"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8491bd2262db4a8c"/>
   </x:sheets>
 </x:workbook>
 </file>
